--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_sodium/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Major_and_trace_elements_total__Total_sodium.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_sodium/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Major_and_trace_elements_total__Total_sodium.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M293"/>
+  <dimension ref="A1:L293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -440,8 +440,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,11 +501,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>source_row</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
@@ -524,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -557,12 +551,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -579,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -612,12 +603,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -634,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,12 +655,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -689,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -722,12 +707,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -744,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -777,12 +759,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -799,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -832,12 +811,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -854,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -887,12 +863,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -909,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -942,12 +915,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -964,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -997,12 +967,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1019,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1052,12 +1019,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1107,12 +1071,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1162,12 +1123,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1217,12 +1175,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1272,12 +1227,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1327,12 +1279,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1382,12 +1331,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1437,12 +1383,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1492,12 +1435,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1547,12 +1487,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1602,12 +1539,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1657,12 +1591,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1712,12 +1643,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1767,12 +1695,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1822,12 +1747,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1877,12 +1799,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1932,12 +1851,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1987,12 +1903,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2009,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2042,12 +1955,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2064,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2097,12 +2007,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2152,12 +2059,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2207,12 +2111,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2262,12 +2163,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2317,12 +2215,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2372,12 +2267,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2427,12 +2319,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2482,12 +2371,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2537,12 +2423,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2592,12 +2475,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2647,12 +2527,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2702,12 +2579,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2757,12 +2631,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2812,12 +2683,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2867,12 +2735,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2922,12 +2787,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2977,12 +2839,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3032,12 +2891,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3054,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3087,12 +2943,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3109,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3142,12 +2995,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3197,12 +3047,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3252,12 +3099,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3307,12 +3151,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3362,12 +3203,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3417,12 +3255,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3439,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3472,12 +3307,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3527,12 +3359,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3582,12 +3411,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="n">
-        <v>203</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3637,12 +3463,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="n">
-        <v>235</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3692,12 +3515,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="n">
-        <v>236</v>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3747,12 +3567,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3802,12 +3619,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="n">
-        <v>253</v>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3857,12 +3671,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="n">
-        <v>254</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3912,12 +3723,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3967,12 +3775,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="n">
-        <v>256</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4022,12 +3827,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4044,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4077,12 +3879,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4099,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4132,12 +3931,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="n">
-        <v>259</v>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4154,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4187,12 +3983,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4209,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4242,12 +4035,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="n">
-        <v>261</v>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4297,12 +4087,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="n">
-        <v>262</v>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4352,12 +4139,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4407,12 +4191,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4462,12 +4243,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="n">
-        <v>265</v>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4517,12 +4295,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4572,12 +4347,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="n">
-        <v>267</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4627,12 +4399,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4682,12 +4451,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="n">
-        <v>273</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4737,12 +4503,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="n">
-        <v>274</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4792,12 +4555,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="n">
-        <v>289</v>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4847,12 +4607,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="n">
-        <v>290</v>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4869,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4902,12 +4659,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="n">
-        <v>291</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4957,12 +4711,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5012,12 +4763,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="n">
-        <v>293</v>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5034,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5067,12 +4815,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="n">
-        <v>294</v>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5089,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5122,12 +4867,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5144,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5177,12 +4919,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="n">
-        <v>296</v>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5199,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5232,12 +4971,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5254,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5287,12 +5023,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5342,12 +5075,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="n">
-        <v>299</v>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5397,12 +5127,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5419,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5452,12 +5179,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5507,12 +5231,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5562,12 +5283,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="n">
-        <v>305</v>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5617,12 +5335,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="n">
-        <v>306</v>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5672,12 +5387,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="n">
-        <v>321</v>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5727,12 +5439,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="n">
-        <v>322</v>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5749,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5782,12 +5491,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="n">
-        <v>323</v>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5837,12 +5543,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="n">
-        <v>324</v>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5892,12 +5595,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5947,12 +5647,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="n">
-        <v>326</v>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6002,12 +5699,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6024,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6057,12 +5751,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="n">
-        <v>328</v>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6079,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6112,12 +5803,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="n">
-        <v>329</v>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6134,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6167,12 +5855,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="n">
-        <v>330</v>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6189,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6222,12 +5907,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="n">
-        <v>331</v>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6244,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6277,12 +5959,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6299,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6332,12 +6011,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="n">
-        <v>333</v>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6387,12 +6063,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6442,12 +6115,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6134,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6497,12 +6167,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6186,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6552,12 +6219,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6238,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6607,12 +6271,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="n">
-        <v>341</v>
-      </c>
-      <c r="M112" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6290,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6662,12 +6323,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="M113" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6342,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6717,12 +6375,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="n">
-        <v>357</v>
-      </c>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6394,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6772,12 +6427,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="n">
-        <v>358</v>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6446,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6827,12 +6479,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="n">
-        <v>359</v>
-      </c>
-      <c r="M116" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6498,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6882,12 +6531,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="n">
-        <v>360</v>
-      </c>
-      <c r="M117" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6904,12 +6550,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6937,12 +6583,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="n">
-        <v>361</v>
-      </c>
-      <c r="M118" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6602,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6992,12 +6635,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="n">
-        <v>362</v>
-      </c>
-      <c r="M119" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7014,12 +6654,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -7047,12 +6687,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="n">
-        <v>363</v>
-      </c>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7069,12 +6706,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7102,12 +6739,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="n">
-        <v>364</v>
-      </c>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7124,12 +6758,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7157,12 +6791,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7179,12 +6810,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7212,12 +6843,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="n">
-        <v>366</v>
-      </c>
-      <c r="M123" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7234,12 +6862,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7267,12 +6895,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="n">
-        <v>367</v>
-      </c>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7289,12 +6914,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7322,12 +6947,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="n">
-        <v>368</v>
-      </c>
-      <c r="M125" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7344,12 +6966,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7377,12 +6999,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="n">
-        <v>369</v>
-      </c>
-      <c r="M126" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7399,12 +7018,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7432,12 +7051,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="n">
-        <v>370</v>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7070,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7487,12 +7103,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="n">
-        <v>371</v>
-      </c>
-      <c r="M128" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7509,12 +7122,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7542,12 +7155,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="n">
-        <v>372</v>
-      </c>
-      <c r="M129" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7174,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7597,12 +7207,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="n">
-        <v>373</v>
-      </c>
-      <c r="M130" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7226,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7652,12 +7259,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="n">
-        <v>376</v>
-      </c>
-      <c r="M131" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7278,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7707,12 +7311,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="n">
-        <v>377</v>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7729,12 +7330,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7762,12 +7363,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="n">
-        <v>392</v>
-      </c>
-      <c r="M133" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7382,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7817,12 +7415,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="n">
-        <v>393</v>
-      </c>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7839,12 +7434,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7872,12 +7467,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="n">
-        <v>394</v>
-      </c>
-      <c r="M135" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7486,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7927,12 +7519,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="n">
-        <v>395</v>
-      </c>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7538,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7982,12 +7571,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="n">
-        <v>396</v>
-      </c>
-      <c r="M137" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8004,12 +7590,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -8037,12 +7623,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="n">
-        <v>397</v>
-      </c>
-      <c r="M138" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8059,12 +7642,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -8092,12 +7675,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="n">
-        <v>398</v>
-      </c>
-      <c r="M139" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8114,12 +7694,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -8147,12 +7727,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="n">
-        <v>399</v>
-      </c>
-      <c r="M140" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8169,12 +7746,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -8202,12 +7779,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="M141" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8224,12 +7798,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -8257,12 +7831,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="n">
-        <v>401</v>
-      </c>
-      <c r="M142" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8279,12 +7850,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -8312,12 +7883,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="n">
-        <v>402</v>
-      </c>
-      <c r="M143" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8334,12 +7902,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -8367,12 +7935,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="n">
-        <v>403</v>
-      </c>
-      <c r="M144" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8389,12 +7954,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8422,12 +7987,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="M145" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8006,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8477,12 +8039,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="n">
-        <v>405</v>
-      </c>
-      <c r="M146" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8058,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8532,12 +8091,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="M147" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8110,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8587,12 +8143,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="n">
-        <v>411</v>
-      </c>
-      <c r="M148" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8162,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8642,12 +8195,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="2" t="n">
-        <v>412</v>
-      </c>
-      <c r="M149" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8664,12 +8214,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8697,12 +8247,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="n">
-        <v>413</v>
-      </c>
-      <c r="M150" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8266,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8752,12 +8299,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="M151" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8318,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8807,12 +8351,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="n">
-        <v>428</v>
-      </c>
-      <c r="M152" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8829,12 +8370,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8862,12 +8403,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="M153" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8422,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8917,12 +8455,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="M154" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8474,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8972,12 +8507,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="n">
-        <v>431</v>
-      </c>
-      <c r="M155" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8994,12 +8526,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -9027,12 +8559,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="n">
-        <v>432</v>
-      </c>
-      <c r="M156" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9049,12 +8578,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -9082,12 +8611,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="n">
-        <v>433</v>
-      </c>
-      <c r="M157" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9104,12 +8630,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -9137,12 +8663,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="n">
-        <v>434</v>
-      </c>
-      <c r="M158" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9159,12 +8682,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -9192,12 +8715,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="n">
-        <v>435</v>
-      </c>
-      <c r="M159" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9214,12 +8734,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9247,12 +8767,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="n">
-        <v>436</v>
-      </c>
-      <c r="M160" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9269,12 +8786,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -9302,12 +8819,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="2" t="n">
-        <v>437</v>
-      </c>
-      <c r="M161" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8838,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -9357,12 +8871,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="n">
-        <v>438</v>
-      </c>
-      <c r="M162" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9379,12 +8890,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -9412,12 +8923,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="M163" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9434,12 +8942,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -9467,12 +8975,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="n">
-        <v>440</v>
-      </c>
-      <c r="M164" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9489,12 +8994,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9522,12 +9027,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="M165" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9544,12 +9046,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9577,12 +9079,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="n">
-        <v>442</v>
-      </c>
-      <c r="M166" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9098,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9632,12 +9131,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="n">
-        <v>443</v>
-      </c>
-      <c r="M167" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9654,12 +9150,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9687,12 +9183,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="M168" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9202,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9742,12 +9235,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="2" t="n">
-        <v>446</v>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9254,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9797,12 +9287,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="n">
-        <v>461</v>
-      </c>
-      <c r="M170" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9306,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9852,12 +9339,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9874,12 +9358,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9907,12 +9391,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="n">
-        <v>463</v>
-      </c>
-      <c r="M172" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9410,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9962,12 +9443,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="n">
-        <v>464</v>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9984,12 +9462,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -10017,12 +9495,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="n">
-        <v>465</v>
-      </c>
-      <c r="M174" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10039,12 +9514,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -10072,12 +9547,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="n">
-        <v>466</v>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10094,12 +9566,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -10127,12 +9599,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="n">
-        <v>467</v>
-      </c>
-      <c r="M176" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10149,12 +9618,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -10182,12 +9651,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="n">
-        <v>468</v>
-      </c>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10204,12 +9670,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -10237,12 +9703,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="n">
-        <v>469</v>
-      </c>
-      <c r="M178" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10259,12 +9722,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -10292,12 +9755,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="n">
-        <v>470</v>
-      </c>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10314,12 +9774,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -10347,12 +9807,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="n">
-        <v>471</v>
-      </c>
-      <c r="M180" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10369,12 +9826,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -10402,12 +9859,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="n">
-        <v>472</v>
-      </c>
-      <c r="M181" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10424,12 +9878,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -10457,12 +9911,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="2" t="n">
-        <v>473</v>
-      </c>
-      <c r="M182" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10479,12 +9930,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -10512,12 +9963,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="n">
-        <v>474</v>
-      </c>
-      <c r="M183" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10534,12 +9982,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10567,12 +10015,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="2" t="n">
-        <v>475</v>
-      </c>
-      <c r="M184" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10034,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10622,12 +10067,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="2" t="n">
-        <v>476</v>
-      </c>
-      <c r="M185" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10086,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10677,12 +10119,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="n">
-        <v>481</v>
-      </c>
-      <c r="M186" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10138,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10732,12 +10171,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="2" t="n">
-        <v>482</v>
-      </c>
-      <c r="M187" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10190,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10787,12 +10223,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="2" t="n">
-        <v>483</v>
-      </c>
-      <c r="M188" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10242,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10842,12 +10275,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="2" t="n">
-        <v>484</v>
-      </c>
-      <c r="M189" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10864,12 +10294,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10897,12 +10327,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="n">
-        <v>496</v>
-      </c>
-      <c r="M190" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10919,12 +10346,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10952,12 +10379,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="2" t="n">
-        <v>497</v>
-      </c>
-      <c r="M191" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10398,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -11007,12 +10431,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="n">
-        <v>498</v>
-      </c>
-      <c r="M192" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11029,12 +10450,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -11062,12 +10483,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="2" t="n">
-        <v>499</v>
-      </c>
-      <c r="M193" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11084,12 +10502,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -11117,12 +10535,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="M194" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11139,12 +10554,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -11172,12 +10587,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="2" t="n">
-        <v>501</v>
-      </c>
-      <c r="M195" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11194,12 +10606,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -11227,12 +10639,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="n">
-        <v>502</v>
-      </c>
-      <c r="M196" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11249,12 +10658,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -11282,12 +10691,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="M197" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11304,12 +10710,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -11337,12 +10743,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="M198" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11359,12 +10762,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -11392,12 +10795,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="M199" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11414,12 +10814,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -11447,12 +10847,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="2" t="n">
-        <v>506</v>
-      </c>
-      <c r="M200" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11469,12 +10866,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -11502,12 +10899,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="2" t="n">
-        <v>507</v>
-      </c>
-      <c r="M201" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11524,12 +10918,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -11557,12 +10951,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="n">
-        <v>512</v>
-      </c>
-      <c r="M202" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11579,12 +10970,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11612,12 +11003,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="2" t="n">
-        <v>513</v>
-      </c>
-      <c r="M203" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11634,12 +11022,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11667,12 +11055,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="2" t="n">
-        <v>514</v>
-      </c>
-      <c r="M204" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11689,12 +11074,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11722,12 +11107,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="2" t="n">
-        <v>515</v>
-      </c>
-      <c r="M205" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11744,12 +11126,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11777,12 +11159,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="M206" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11799,12 +11178,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11832,12 +11211,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="2" t="n">
-        <v>530</v>
-      </c>
-      <c r="M207" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11854,12 +11230,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11887,12 +11263,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="2" t="n">
-        <v>531</v>
-      </c>
-      <c r="M208" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11909,12 +11282,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11942,12 +11315,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="2" t="n">
-        <v>532</v>
-      </c>
-      <c r="M209" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11964,12 +11334,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11997,12 +11367,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="M210" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12019,12 +11386,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -12052,12 +11419,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="n">
-        <v>534</v>
-      </c>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12074,12 +11438,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -12107,12 +11471,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="n">
-        <v>535</v>
-      </c>
-      <c r="M212" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12129,12 +11490,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -12162,12 +11523,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="n">
-        <v>536</v>
-      </c>
-      <c r="M213" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12184,12 +11542,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -12217,12 +11575,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K214" s="2" t="inlineStr"/>
-      <c r="L214" s="2" t="n">
-        <v>537</v>
-      </c>
-      <c r="M214" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12239,12 +11594,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -12272,12 +11627,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="n">
-        <v>538</v>
-      </c>
-      <c r="M215" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12294,12 +11646,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -12327,12 +11679,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K216" s="2" t="inlineStr"/>
-      <c r="L216" s="2" t="n">
-        <v>539</v>
-      </c>
-      <c r="M216" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12349,12 +11698,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -12382,12 +11731,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K217" s="2" t="inlineStr"/>
-      <c r="L217" s="2" t="n">
-        <v>540</v>
-      </c>
-      <c r="M217" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12404,12 +11750,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -12437,12 +11783,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="n">
-        <v>541</v>
-      </c>
-      <c r="M218" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12459,12 +11802,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -12492,12 +11835,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K219" s="2" t="inlineStr"/>
-      <c r="L219" s="2" t="n">
-        <v>542</v>
-      </c>
-      <c r="M219" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12514,12 +11854,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -12547,12 +11887,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="n">
-        <v>543</v>
-      </c>
-      <c r="M220" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12569,12 +11906,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -12602,12 +11939,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="n">
-        <v>548</v>
-      </c>
-      <c r="M221" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12624,12 +11958,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12657,12 +11991,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="2" t="n">
-        <v>549</v>
-      </c>
-      <c r="M222" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12679,12 +12010,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12712,12 +12043,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="M223" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12062,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12767,12 +12095,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="n">
-        <v>551</v>
-      </c>
-      <c r="M224" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12789,12 +12114,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12822,12 +12147,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="n">
-        <v>565</v>
-      </c>
-      <c r="M225" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12844,12 +12166,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12877,12 +12199,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="2" t="n">
-        <v>566</v>
-      </c>
-      <c r="M226" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12899,12 +12218,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12932,12 +12251,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="2" t="n">
-        <v>567</v>
-      </c>
-      <c r="M227" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12270,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12987,12 +12303,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="n">
-        <v>568</v>
-      </c>
-      <c r="M228" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13009,12 +12322,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -13042,12 +12355,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="n">
-        <v>569</v>
-      </c>
-      <c r="M229" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13064,12 +12374,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -13097,12 +12407,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K230" s="2" t="inlineStr"/>
-      <c r="L230" s="2" t="n">
-        <v>570</v>
-      </c>
-      <c r="M230" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13119,12 +12426,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -13152,12 +12459,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="M231" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13174,12 +12478,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -13207,12 +12511,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K232" s="2" t="inlineStr"/>
-      <c r="L232" s="2" t="n">
-        <v>572</v>
-      </c>
-      <c r="M232" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13229,12 +12530,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -13262,12 +12563,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="2" t="n">
-        <v>573</v>
-      </c>
-      <c r="M233" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13284,12 +12582,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -13317,12 +12615,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="2" t="n">
-        <v>574</v>
-      </c>
-      <c r="M234" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13339,12 +12634,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -13372,12 +12667,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="n">
-        <v>575</v>
-      </c>
-      <c r="M235" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13394,12 +12686,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -13427,12 +12719,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="n">
-        <v>576</v>
-      </c>
-      <c r="M236" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13449,12 +12738,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -13482,12 +12771,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="n">
-        <v>577</v>
-      </c>
-      <c r="M237" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13504,12 +12790,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -13537,12 +12823,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="2" t="n">
-        <v>578</v>
-      </c>
-      <c r="M238" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13559,12 +12842,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -13592,12 +12875,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="M239" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13614,12 +12894,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -13647,12 +12927,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="2" t="n">
-        <v>583</v>
-      </c>
-      <c r="M240" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13669,12 +12946,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -13702,12 +12979,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="2" t="n">
-        <v>584</v>
-      </c>
-      <c r="M241" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13724,12 +12998,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13757,12 +13031,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K242" s="2" t="inlineStr"/>
-      <c r="L242" s="2" t="n">
-        <v>599</v>
-      </c>
-      <c r="M242" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13779,12 +13050,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13812,12 +13083,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K243" s="2" t="inlineStr"/>
-      <c r="L243" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="M243" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13834,12 +13102,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13867,12 +13135,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K244" s="2" t="inlineStr"/>
-      <c r="L244" s="2" t="n">
-        <v>601</v>
-      </c>
-      <c r="M244" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13889,12 +13154,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13922,12 +13187,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="2" t="n">
-        <v>602</v>
-      </c>
-      <c r="M245" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13944,12 +13206,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13977,12 +13239,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K246" s="2" t="inlineStr"/>
-      <c r="L246" s="2" t="n">
-        <v>603</v>
-      </c>
-      <c r="M246" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13999,12 +13258,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -14032,12 +13291,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K247" s="2" t="inlineStr"/>
-      <c r="L247" s="2" t="n">
-        <v>604</v>
-      </c>
-      <c r="M247" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14054,12 +13310,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -14087,12 +13343,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K248" s="2" t="inlineStr"/>
-      <c r="L248" s="2" t="n">
-        <v>605</v>
-      </c>
-      <c r="M248" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14109,12 +13362,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -14142,12 +13395,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K249" s="2" t="inlineStr"/>
-      <c r="L249" s="2" t="n">
-        <v>606</v>
-      </c>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14164,12 +13414,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -14197,12 +13447,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K250" s="2" t="inlineStr"/>
-      <c r="L250" s="2" t="n">
-        <v>607</v>
-      </c>
-      <c r="M250" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14219,12 +13466,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -14252,12 +13499,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K251" s="2" t="inlineStr"/>
-      <c r="L251" s="2" t="n">
-        <v>608</v>
-      </c>
-      <c r="M251" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14274,12 +13518,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -14307,12 +13551,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="n">
-        <v>609</v>
-      </c>
-      <c r="M252" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14329,12 +13570,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -14362,12 +13603,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="n">
-        <v>610</v>
-      </c>
-      <c r="M253" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14384,12 +13622,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -14417,12 +13655,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K254" s="2" t="inlineStr"/>
-      <c r="L254" s="2" t="n">
-        <v>611</v>
-      </c>
-      <c r="M254" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14439,12 +13674,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -14472,12 +13707,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K255" s="2" t="inlineStr"/>
-      <c r="L255" s="2" t="n">
-        <v>612</v>
-      </c>
-      <c r="M255" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14494,12 +13726,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -14527,12 +13759,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="n">
-        <v>613</v>
-      </c>
-      <c r="M256" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14549,12 +13778,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -14582,12 +13811,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K257" s="2" t="inlineStr"/>
-      <c r="L257" s="2" t="n">
-        <v>614</v>
-      </c>
-      <c r="M257" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14604,12 +13830,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -14637,12 +13863,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K258" s="2" t="inlineStr"/>
-      <c r="L258" s="2" t="n">
-        <v>618</v>
-      </c>
-      <c r="M258" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14659,12 +13882,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -14692,12 +13915,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="2" t="n">
-        <v>619</v>
-      </c>
-      <c r="M259" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14714,12 +13934,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -14747,12 +13967,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K260" s="2" t="inlineStr"/>
-      <c r="L260" s="2" t="n">
-        <v>620</v>
-      </c>
-      <c r="M260" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14769,12 +13986,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14802,12 +14019,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K261" s="2" t="inlineStr"/>
-      <c r="L261" s="2" t="n">
-        <v>634</v>
-      </c>
-      <c r="M261" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14824,12 +14038,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14857,12 +14071,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K262" s="2" t="inlineStr"/>
-      <c r="L262" s="2" t="n">
-        <v>635</v>
-      </c>
-      <c r="M262" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14879,12 +14090,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14912,12 +14123,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K263" s="2" t="inlineStr"/>
-      <c r="L263" s="2" t="n">
-        <v>636</v>
-      </c>
-      <c r="M263" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14934,12 +14142,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14967,12 +14175,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K264" s="2" t="inlineStr"/>
-      <c r="L264" s="2" t="n">
-        <v>637</v>
-      </c>
-      <c r="M264" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14989,12 +14194,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -15022,12 +14227,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K265" s="2" t="inlineStr"/>
-      <c r="L265" s="2" t="n">
-        <v>638</v>
-      </c>
-      <c r="M265" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15044,12 +14246,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -15077,12 +14279,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K266" s="2" t="inlineStr"/>
-      <c r="L266" s="2" t="n">
-        <v>639</v>
-      </c>
-      <c r="M266" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15099,12 +14298,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -15132,12 +14331,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K267" s="2" t="inlineStr"/>
-      <c r="L267" s="2" t="n">
-        <v>640</v>
-      </c>
-      <c r="M267" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15154,12 +14350,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -15187,12 +14383,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K268" s="2" t="inlineStr"/>
-      <c r="L268" s="2" t="n">
-        <v>641</v>
-      </c>
-      <c r="M268" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15209,12 +14402,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -15242,12 +14435,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K269" s="2" t="inlineStr"/>
-      <c r="L269" s="2" t="n">
-        <v>642</v>
-      </c>
-      <c r="M269" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15264,12 +14454,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -15297,12 +14487,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K270" s="2" t="inlineStr"/>
-      <c r="L270" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="M270" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15319,12 +14506,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -15352,12 +14539,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K271" s="2" t="inlineStr"/>
-      <c r="L271" s="2" t="n">
-        <v>644</v>
-      </c>
-      <c r="M271" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15374,12 +14558,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -15407,12 +14591,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K272" s="2" t="inlineStr"/>
-      <c r="L272" s="2" t="n">
-        <v>645</v>
-      </c>
-      <c r="M272" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15429,12 +14610,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -15462,12 +14643,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K273" s="2" t="inlineStr"/>
-      <c r="L273" s="2" t="n">
-        <v>646</v>
-      </c>
-      <c r="M273" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15484,12 +14662,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -15517,12 +14695,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K274" s="2" t="inlineStr"/>
-      <c r="L274" s="2" t="n">
-        <v>647</v>
-      </c>
-      <c r="M274" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15539,12 +14714,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -15572,12 +14747,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K275" s="2" t="inlineStr"/>
-      <c r="L275" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="M275" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15594,12 +14766,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -15627,12 +14799,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K276" s="2" t="inlineStr"/>
-      <c r="L276" s="2" t="n">
-        <v>649</v>
-      </c>
-      <c r="M276" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15649,12 +14818,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -15682,12 +14851,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
-      <c r="L277" s="2" t="n">
-        <v>652</v>
-      </c>
-      <c r="M277" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15704,12 +14870,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -15737,12 +14903,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
-      <c r="L278" s="2" t="n">
-        <v>653</v>
-      </c>
-      <c r="M278" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15759,12 +14922,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -15792,12 +14955,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
-      <c r="L279" s="2" t="n">
-        <v>668</v>
-      </c>
-      <c r="M279" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15814,12 +14974,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -15847,12 +15007,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
-      <c r="L280" s="2" t="n">
-        <v>669</v>
-      </c>
-      <c r="M280" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15026,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -15902,12 +15059,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
-      <c r="L281" s="2" t="n">
-        <v>670</v>
-      </c>
-      <c r="M281" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15924,12 +15078,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -15957,12 +15111,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
-      <c r="L282" s="2" t="n">
-        <v>671</v>
-      </c>
-      <c r="M282" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15979,12 +15130,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -16012,12 +15163,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
-      <c r="L283" s="2" t="n">
-        <v>672</v>
-      </c>
-      <c r="M283" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16034,12 +15182,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -16067,12 +15215,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
-      <c r="L284" s="2" t="n">
-        <v>673</v>
-      </c>
-      <c r="M284" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16089,12 +15234,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -16122,12 +15267,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
-      <c r="L285" s="2" t="n">
-        <v>674</v>
-      </c>
-      <c r="M285" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16144,12 +15286,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -16177,12 +15319,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
-      <c r="L286" s="2" t="n">
-        <v>675</v>
-      </c>
-      <c r="M286" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16199,12 +15338,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -16232,12 +15371,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
-      <c r="L287" s="2" t="n">
-        <v>676</v>
-      </c>
-      <c r="M287" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16254,12 +15390,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -16287,12 +15423,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
-      <c r="L288" s="2" t="n">
-        <v>677</v>
-      </c>
-      <c r="M288" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16309,12 +15442,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -16342,12 +15475,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K289" s="2" t="inlineStr"/>
-      <c r="L289" s="2" t="n">
-        <v>678</v>
-      </c>
-      <c r="M289" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16364,12 +15494,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -16397,12 +15527,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K290" s="2" t="inlineStr"/>
-      <c r="L290" s="2" t="n">
-        <v>679</v>
-      </c>
-      <c r="M290" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16419,12 +15546,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -16452,12 +15579,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K291" s="2" t="inlineStr"/>
-      <c r="L291" s="2" t="n">
-        <v>680</v>
-      </c>
-      <c r="M291" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16474,12 +15598,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -16507,12 +15631,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K292" s="2" t="inlineStr"/>
-      <c r="L292" s="2" t="n">
-        <v>681</v>
-      </c>
-      <c r="M292" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16529,12 +15650,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -16562,12 +15683,9 @@
         <v>-93.45328000000001</v>
       </c>
       <c r="K293" s="2" t="inlineStr"/>
-      <c r="L293" s="2" t="n">
-        <v>682</v>
-      </c>
-      <c r="M293" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Na (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
